--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.06205511021942</v>
+        <v>9.272583955410656</v>
       </c>
       <c r="D2" t="n">
-        <v>12.94736361620126</v>
+        <v>2.103946587632704</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4127623383181813</v>
+        <v>0.06707387997670455</v>
       </c>
       <c r="F2" t="n">
-        <v>6.330230129091927</v>
+        <v>1.028662395977438</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.88757978685578</v>
+        <v>9.406731715364065</v>
       </c>
       <c r="D3" t="n">
-        <v>25.60782387438511</v>
+        <v>4.161271379587581</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4127623383181813</v>
+        <v>0.06707387997670455</v>
       </c>
       <c r="F3" t="n">
-        <v>6.330230129091927</v>
+        <v>1.028662395977438</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
